--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
@@ -466,18 +466,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.007363531664955847</v>
+        <v>0.08178693972748619</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.02977185850050446</v>
+        <v>0.1058507801881154</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.2583592943268546</v>
+        <v>0.2246874117619884</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.225303890741113</v>
+        <v>0.1978146071816885</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.1032508421213568</v>
+        <v>0.440915034618833</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.1451605495312766</v>
+        <v>0.6467403321710453</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.223199988020069</v>
+        <v>0.6201769964739671</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.148909452771786</v>
+        <v>0.1590592213122745</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1236402476882125</v>
+        <v>0.1066955128359608</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.05590710636418326</v>
+        <v>0.5840791949612462</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>26.92025564613633</v>
+        <v>20.18532564974657</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2495991746306522</v>
+        <v>-0.1371040764044242</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.03101890971773069</v>
+        <v>0.1142442872903577</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2094021738509181</v>
+        <v>0.1607285394457139</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1955989447924083</v>
+        <v>0.1658432086687044</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-1.394104631124534</v>
+        <v>-0.9677325043922336</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.892820913803564</v>
+        <v>-1.331538004800688</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-0.1669477306080866</v>
+        <v>0.6254793863328633</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2769077974177049</v>
+        <v>0.1604274211926697</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.173430386603639</v>
+        <v>0.09856586197079198</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.9333450484606625</v>
+        <v>-0.8872927756020915</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>23.47252923918749</v>
+        <v>17.03350764115118</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.01718637365716347</v>
+        <v>-0.0802623502571741</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.1094832324709121</v>
+        <v>0.03827772968413323</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2233655187077581</v>
+        <v>0.153959140551835</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1969636771385239</v>
+        <v>0.1344538822490397</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.03672812655139977</v>
+        <v>-0.5857256649910058</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.05602740926734275</v>
+        <v>-0.8122915510553034</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.6284134012874076</v>
+        <v>0.3108916651467194</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.209847976894352</v>
+        <v>0.1965084256211178</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.09260157319740459</v>
+        <v>0.07353350503179723</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.08525297484069869</v>
+        <v>-0.4245959139636017</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>24.14677986713315</v>
+        <v>18.35707534534669</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1291669627922051</v>
+        <v>0.0307206802950204</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2292197528222699</v>
+        <v>-0.08770211190388755</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2311486272681887</v>
+        <v>0.2130899734908673</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1745149882619987</v>
+        <v>0.132192920039864</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.5725372844671412</v>
+        <v>0.1820477509689744</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.8196116681550927</v>
+        <v>0.3131510862551459</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.548268748337829</v>
+        <v>-0.7493770817698518</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2580763964632468</v>
+        <v>0.1801065807177068</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3360699126314611</v>
+        <v>0.1737339348381576</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.5197284727400669</v>
+        <v>0.1777294216864797</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>25.17340772909411</v>
+        <v>18.01414474985948</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2916740105895128</v>
+        <v>0.1835769673054117</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.05501312955401683</v>
+        <v>-0.03327834259431983</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2754370588775948</v>
+        <v>0.2004692966576004</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2013485428365092</v>
+        <v>0.1213604588207766</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.047755342394988</v>
+        <v>0.8979940627837055</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.495908235961057</v>
+        <v>1.286815667668958</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.3946903720759087</v>
+        <v>-0.2397822219632746</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1981365456164503</v>
+        <v>0.1358761392518996</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1823185022338726</v>
+        <v>0.1222117052919502</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.534175804984136</v>
+        <v>1.405605709832878</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>28.0625768258167</v>
+        <v>22.02202742195214</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1692039370017415</v>
+        <v>0.1459769598116909</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1870590073281779</v>
+        <v>0.1634773278504653</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.4127192467331187</v>
+        <v>0.2652705900089265</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3466796411034733</v>
+        <v>0.2014325077866864</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.8625351210395812</v>
+        <v>1.014876507319138</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.21280383334758</v>
+        <v>1.399090600122807</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.073926957201763</v>
+        <v>1.417550025455008</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1904468921684758</v>
+        <v>0.1124336192226177</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.194984055120777</v>
+        <v>0.09087063135719731</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.734726888978019</v>
+        <v>2.512670889052949</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>28.25202743741331</v>
+        <v>20.59025610160578</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
@@ -468,16 +468,16 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.08178693972748619</v>
+        <v>-0.03550059924510052</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1058507801881154</v>
+        <v>-0.01404576479314801</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.2246874117619884</v>
+        <v>0.2542965037762901</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1978146071816885</v>
+        <v>0.2446119598156732</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.440915034618833</v>
+        <v>-0.09253083537433239</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.6467403321710453</v>
+        <v>-0.1317136023058287</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.6201769964739671</v>
+        <v>0.0003341744943032855</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1590592213122745</v>
+        <v>0.1822222949939624</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1066955128359608</v>
+        <v>0.1766406713637559</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.5840791949612462</v>
+        <v>-0.2196421438568917</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>20.18532564974657</v>
+        <v>21.07760695656944</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1371040764044242</v>
+        <v>-0.1527258325661632</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.1142442872903577</v>
+        <v>0.09407215287103132</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.1607285394457139</v>
+        <v>0.1984095169296628</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1658432086687044</v>
+        <v>0.1919061877510348</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9677325043922336</v>
+        <v>-0.8456629859620559</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.331538004800688</v>
+        <v>-1.151233558231645</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.6254793863328633</v>
+        <v>0.4767233247285417</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1604274211926697</v>
+        <v>0.2205035102278902</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.09856586197079198</v>
+        <v>0.1151689865860936</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8872927756020915</v>
+        <v>-0.7188478296419708</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>17.03350764115118</v>
+        <v>18.01711228943114</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.0802623502571741</v>
+        <v>-0.1083102264431312</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.03827772968413323</v>
+        <v>0.006614912339470091</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.153959140551835</v>
+        <v>0.1684868313147463</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1344538822490397</v>
+        <v>0.1454012180853051</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.5857256649910058</v>
+        <v>-0.7127007891409072</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.8122915510553034</v>
+        <v>-0.9905492693649566</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.3108916651467194</v>
+        <v>0.08182678135585746</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.1965084256211178</v>
+        <v>0.1942520468462868</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07353350503179723</v>
+        <v>0.06980794476189067</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.4245959139636017</v>
+        <v>-0.5792692153674682</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>18.35707534534669</v>
+        <v>17.19904078665004</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0307206802950204</v>
+        <v>-0.06919551826081516</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.08770211190388755</v>
+        <v>-0.1761386191669327</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2130899734908673</v>
+        <v>0.2161532356098891</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.132192920039864</v>
+        <v>0.1515685781100759</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1820477509689744</v>
+        <v>-0.3074920760602672</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.3131510862551459</v>
+        <v>-0.459204914192457</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.7493770817698518</v>
+        <v>-1.34803865544349</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1801065807177068</v>
+        <v>0.2218899333167407</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1737339348381576</v>
+        <v>0.2742844088165364</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.1777294216864797</v>
+        <v>-0.3242574545839438</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>18.01414474985948</v>
+        <v>18.28124034590994</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1835769673054117</v>
+        <v>0.05482300561846887</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.03327834259431983</v>
+        <v>-0.1384419666575045</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2004692966576004</v>
+        <v>0.1595335883840818</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1213604588207766</v>
+        <v>0.1246930215363652</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8979940627837055</v>
+        <v>0.3334289780150523</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.286815667668958</v>
+        <v>0.448125114349355</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2397822219632746</v>
+        <v>-1.250488562938754</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1358761392518996</v>
+        <v>0.1166484415956838</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1222117052919502</v>
+        <v>0.2271268675413463</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.405605709832878</v>
+        <v>0.48787808267604</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>22.02202742195214</v>
+        <v>19.05142662039037</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1459769598116909</v>
+        <v>0.06758073441026058</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1634773278504653</v>
+        <v>0.08388390316363092</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.2652705900089265</v>
+        <v>0.2834541545345583</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2014325077866864</v>
+        <v>0.2576433312595027</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.014876507319138</v>
+        <v>0.5106309065094569</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.399090600122807</v>
+        <v>0.7032033792527403</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.417550025455008</v>
+        <v>0.6251441392029029</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1124336192226177</v>
+        <v>0.1501006733548979</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.09087063135719731</v>
+        <v>0.1380111243786685</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.512670889052949</v>
+        <v>0.845031880138668</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>20.59025610160578</v>
+        <v>22.87841938444994</v>
       </c>
     </row>
   </sheetData>
